--- a/input/Domains/Operation/OperationTable.xlsx
+++ b/input/Domains/Operation/OperationTable.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Operation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3102C0CD-5365-B245-B40F-8EE5619D85BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1394F0B-BF69-9441-A02D-FBAEE3303E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="2240" windowWidth="27700" windowHeight="16880" xr2:uid="{87DACAEC-E39F-BC48-BF83-DE9F804BDF9B}"/>
+    <workbookView xWindow="40100" yWindow="580" windowWidth="27700" windowHeight="16880" activeTab="1" xr2:uid="{87DACAEC-E39F-BC48-BF83-DE9F804BDF9B}"/>
   </bookViews>
   <sheets>
     <sheet name="PUSH_REMOTE" sheetId="1" r:id="rId1"/>
+    <sheet name="PUSH_LOCAL" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>pushId</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -90,6 +91,28 @@
   <si>
     <t>test</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push_local_refilled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>push_local_test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titleTextId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bodyTextId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greeting</t>
+  </si>
+  <si>
+    <t>welcome</t>
   </si>
 </sst>
 </file>
@@ -588,4 +611,98 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E51A3-A24E-C749-9D23-F47FDAF206ED}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/input/Domains/Operation/OperationTable.xlsx
+++ b/input/Domains/Operation/OperationTable.xlsx
@@ -1,151 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Operation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1394F0B-BF69-9441-A02D-FBAEE3303E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="40100" yWindow="580" windowWidth="27700" windowHeight="16880" activeTab="1" xr2:uid="{87DACAEC-E39F-BC48-BF83-DE9F804BDF9B}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40100" yWindow="580" windowWidth="27700" windowHeight="16880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PUSH_REMOTE" sheetId="1" r:id="rId1"/>
-    <sheet name="PUSH_LOCAL" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUSH_REMOTE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUSH_LOCAL" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
-  <si>
-    <t>pushId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>topic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>language</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>defaultMsg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>isTest</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pk</t>
-  </si>
-  <si>
-    <t>group:true</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>event</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Korean</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>English</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>push_local_refilled</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>push_local_test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>titleTextId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bodyTextId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>greeting</t>
-  </si>
-  <si>
-    <t>welcome</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -161,29 +59,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -503,206 +460,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBAC27C2-8BE8-DD4F-9C7B-378B5C371132}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="12.85546875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.7109375" style="1"/>
+    <col width="12.85546875" customWidth="1" style="1" min="1" max="2"/>
+    <col width="10.7109375" customWidth="1" style="1" min="3" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>push_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_msg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_test</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>group:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>LOWER(B5&amp;"_"&amp;C5)</f>
+        <v/>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>LOWER(B6&amp;"_"&amp;C6)</f>
+        <v/>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>LOWER(B7&amp;"_"&amp;C7)</f>
+        <v/>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="str">
-        <f>LOWER(B5&amp;"_"&amp;C5)</f>
-        <v>event_korean</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="str">
-        <f>LOWER(B6&amp;"_"&amp;C6)</f>
-        <v>event_english</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="str">
-        <f>LOWER(B7&amp;"_"&amp;C7)</f>
-        <v>test_korean</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="b">
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>LOWER(B8&amp;"_"&amp;C8)</f>
+        <v/>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="str">
-        <f>LOWER(B8&amp;"_"&amp;C8)</f>
-        <v>test_english</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E51A3-A24E-C749-9D23-F47FDAF206ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col width="15.85546875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="b">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>push_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title_text_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>body_text_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_test</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>push_local_refilled</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>welcome</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>push_local_test</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>welcome</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>